--- a/docs/triton-learning/cards/triton-lesson-06-fused-attention-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-06-fused-attention-oral.xlsx
@@ -36,20 +36,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">用 60–90 秒串起分块 Attention 前向。</t>
+          <t xml:space="preserve">请用约 60–90 秒解释分块 Attention 前向：输入 Q/K/V 为 \[B,H,N,D\]，B/H 分别是 batch/head 数，N 是 token 数，D 是特征维度，s 为原始 scale；每个 program 负责一个 head 的 B_M 行 Q，并逐块扫描 B_N 行 K/V。说明它怎样从完整 Attention 公式出发，维护跨块状态并最终写出 O 和供反向使用的 M。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：从完整公式出发，说明一个 program 如何用在线状态得到自己的 O/M。
-• [T#B#数学与分工]：sQKᵀ→按 key softmax→PV；program 固定一个 head 的 Q tile，扫描所需 K/V，独占 O/M 行。
-• [T#B#在线更新]：score tile 是 \[BM,BN\]，acc 是 \[BM,D\]；新最大值出现时同步缩放旧 l 和 acc，再加入本块贡献。
-• [T#B#完成]：最终 O=acc/l；M=m+log₂l 保存完整 log 分母，供反向按块重建 P。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：完整目标是缩放点积、沿 key 归一化、再加权 V；分块实现通过逐行在线状态，得到同一数学输出而不保存完整概率矩阵。
+• [T#B#公式与分工]：每个 head 的计算是 S=sQKᵀ、P=softmax_key(S)、O=PV。一个 program 固定该 head 的一个 Q tile，内部扫描所需 K/V，最后独占对应的输出行。
+• [T#B#形状]：当前分数/权重块是 \[B_M,B_N\]，沿 key 轴归约；输出分子 acc 保留 query 与特征轴，所以是 \[B_M,D\]。每个 query 的 m、l 都是一个标量。
+• [T#B#跨块合并]：先把自然分数 S 换成 x=S/ln2，再用 exp2。m 是当前已见 x 的最大值，l=Σ2^(x−m)，acc 是同一权重下的加权 V 分子。新最大值出现时，要把旧 l 和 acc 同时重标定，再加入新块贡献。
+• [T#B#最终写回]：扫描结束后 O=acc/l。采用 exp2 时保存 M=m+log₂l，即完整分母的 base-2 对数；反向重算同一表示域的 x 后，用 2^(x−M) 恢复局部归一化概率。
+[T#B,!c47f17#边界]：必须始终区分 query、key 和特征轴，以及未归一化的局部指数权重与最终概率；每个 program 的输出所有权贯穿整个扫描。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">完整公式与 key 归一化轴；Q program 的输出所有权；score/acc 的轴语义；m/l/acc 的共同重标定；O 与 M 的最终用途</t>
+          <t xml:space="preserve">写出带原始scale的完整公式，并指出softmax沿key轴；明确一个program固定Q tile、内部扫描K/V并独占输出；正确区分score=\[B_M,B_N\]与acc=\[B_M,D\]；解释m/l/acc的含义及分子分母共同重标定；说明O=acc/l以及M在反向恢复概率中的用途</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -61,20 +63,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">用 60–90 秒串起重算概率的反向。</t>
+          <t xml:space="preserve">请用约 60–90 秒解释所学 Attention 反向的数据流：前向已经从 Q/K/V 得到 O，并保存逐 query 的归一化统计量 M；现在收到损失对 O 的梯度 dO。怎样利用保存量、计算 Delta、按块重建概率，并通过输出分工得到 dQ/dK/dV？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：用保存量重建局部概率，再按各输出的归约方向生成梯度。
-• [T#B#准备]：前向保存 Q/K/V/O/M；反向输入 dO，先以逐行 O·dO 得到 Delta。
-• [T#B#计算]：用 M 重建 P，计算 dP、G=P⊙(dP−Delta)，再得到 dV=PᵀdO、dQ=sGK、dK=sGᵀQ。
-• [T#B#分工]：dQ 固定 query 扫 key；dK/dV 固定 key 扫 query。单个 program 算齐并独占输出块时不需 atomic。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：反向用前向保存量和 dO 重新建立局部概率，再沿每种输出梯度所需的方向归约，避免物化完整的 N×N 中间矩阵。
+• [T#B#保存与准备]：前向保存 Q/K/V/O/M。反向先对每个 query 沿特征维计算 Delta_i=Σ_d O_id*dO_id，结果是一行一个标量；它等于该行 Σ_j P_ij*dP_ij。
+• [T#B#恢复概率]：用 Q/K 重算自然分数 S，再换成 x=S/ln2，以 P=2^(x−M) 恢复对应概率。M 保存的是完整分母的 log₂，不能把它当成仅有行最大值。
+• [T#B#反向链]：由 O=PV 得到 dP=dOVᵀ 和 dV=PᵀdO，再令 G=P⊙(dP−Delta)，即对自然分数 S=sQKᵀ 的梯度，得到 dQ=sGK、dK=sGᵀQ。这里 s 为固定的原始 scale。
+• [T#B#输出所有权]：dQ 固定 query 并沿 key 汇总；dK/dV 固定 key 并沿 query 汇总。一个 program 算齐自己的输出块后独占写回，所以这种分工不需要跨 program atomic。
+[T#B,!c47f17#边界]：前向保存量、反向临时量和最终梯度的产生时间不同。若把同一输出块的归约拆给多个 program，就必须另行合并部分贡献。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">保存量／临时量／输出梯度；Delta 的归约轴与作用；M 重建 P；dP→G→三个梯度；完整归约与独占输出</t>
+          <t xml:space="preserve">按产生时间区分前向保存量、反向临时量与最终梯度；说明Delta沿特征维求和且每query一个值；说明M重建概率而非只代替行最大值；完整说明dP、softmax分数梯度和三个输入梯度的关系；把归约方向与单program完整归约、独占写回联系起来</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-06-fused-attention-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-06-fused-attention-oral.xlsx
@@ -36,22 +36,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒解释分块 Attention 前向：输入 Q/K/V 为 \[B,H,N,D\]，B/H 分别是 batch/head 数，N 是 token 数，D 是特征维度，s 为原始 scale；每个 program 负责一个 head 的 B_M 行 Q，并逐块扫描 B_N 行 K/V。说明它怎样从完整 Attention 公式出发，维护跨块状态并最终写出 O 和供反向使用的 M。</t>
+          <t xml:space="preserve">以 Triton 官方 fused-attention 教程（快照版）为例，向面试官用约 60–90 秒解释分块 Attention 前向：输入 Q/K/V 为 \[B,H,N,D\]，B/H 分别是 batch/head 数，N 是 token 数，D 是特征维度，s 为原始 scale；每个 program 负责一个 head 的 B_M 行 Q，并逐块扫描 B_N 行 K/V。请从完整 Attention 公式出发，说明它怎样维护跨块状态，并最终写出 O 和供反向使用的 M。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：完整目标是缩放点积、沿 key 归一化、再加权 V；分块实现通过逐行在线状态，得到同一数学输出而不保存完整概率矩阵。
-• [T#B#公式与分工]：每个 head 的计算是 S=sQKᵀ、P=softmax_key(S)、O=PV。一个 program 固定该 head 的一个 Q tile，内部扫描所需 K/V，最后独占对应的输出行。
-• [T#B#形状]：当前分数/权重块是 \[B_M,B_N\]，沿 key 轴归约；输出分子 acc 保留 query 与特征轴，所以是 \[B_M,D\]。每个 query 的 m、l 都是一个标量。
-• [T#B#跨块合并]：先把自然分数 S 换成 x=S/ln2，再用 exp2。m 是当前已见 x 的最大值，l=Σ2^(x−m)，acc 是同一权重下的加权 V 分子。新最大值出现时，要把旧 l 和 acc 同时重标定，再加入新块贡献。
-• [T#B#最终写回]：扫描结束后 O=acc/l。采用 exp2 时保存 M=m+log₂l，即完整分母的 base-2 对数；反向重算同一表示域的 x 后，用 2^(x−M) 恢复局部归一化概率。
-[T#B,!c47f17#边界]：必须始终区分 query、key 和特征轴，以及未归一化的局部指数权重与最终概率；每个 program 的输出所有权贯穿整个扫描。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：分块实现与完整公式算的是同一个输出，只是靠逐行在线状态避免保存完整的概率矩阵。
+• [T#B#公式与分工]：每个 head 算 S=sQKᵀ、P=softmax_key(S)、O=PV。一个 program 固定一个 Q tile，在内部逐块扫描 K/V，并独占对应的输出行。
+• [T#B#形状]：分数块是 \[B_M,B_N\]，沿 key 轴归约；acc 保留 query 与特征轴，是 \[B_M,D\]；每个 query 的 m、l 各是一个标量。
+• [T#B#跨块合并]：分数先换成 x=S/ln2 再用 exp2。m 是已见 x 的最大值，l=Σ2^(x−m)，acc 是同一权重下的加权 V；出现新最大值时，旧 l 与 acc 乘同一个 alpha，再加入新块。
+• [T#B#最终写回]：扫描结束写出 O=acc/l，并保存 M=m+log₂l，即完整分母的 log₂；反向用 2^(x−M) 恢复概率。
+[T#B,!c47f17#边界]：全程要分清 query、key、特征三根轴，以及未归一化的局部权重与最终概率。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">写出带原始scale的完整公式，并指出softmax沿key轴；明确一个program固定Q tile、内部扫描K/V并独占输出；正确区分score=\[B_M,B_N\]与acc=\[B_M,D\]；解释m/l/acc的含义及分子分母共同重标定；说明O=acc/l以及M在反向恢复概率中的用途</t>
+          <t xml:space="preserve">写出带原始 scale 的完整公式，并指出 softmax 沿 key 轴；明确一个 program 固定 Q tile、内部扫描 K/V 并独占输出；正确区分 score=\[B_M,B_N\] 与 acc=\[B_M,D\]；解释 m/l/acc 的含义及分子分母共同重标定；说明 O=acc/l 以及 M 在反向恢复概率中的用途</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -63,22 +63,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒解释所学 Attention 反向的数据流：前向已经从 Q/K/V 得到 O，并保存逐 query 的归一化统计量 M；现在收到损失对 O 的梯度 dO。怎样利用保存量、计算 Delta、按块重建概率，并通过输出分工得到 dQ/dK/dV？</t>
+          <t xml:space="preserve">以 Triton 官方 fused-attention 教程（快照版）为例，向面试官在 90 秒内解释 Attention 反向的数据流：前向已由 Q/K/V 得到 O，并为每个 query 保存归一化统计量 M；现在收到损失对 O 的梯度 dO。请说明怎样利用保存量、计算 Delta、按块重建概率，并通过输出分工得到 dQ/dK/dV。</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：反向用前向保存量和 dO 重新建立局部概率，再沿每种输出梯度所需的方向归约，避免物化完整的 N×N 中间矩阵。
-• [T#B#保存与准备]：前向保存 Q/K/V/O/M。反向先对每个 query 沿特征维计算 Delta_i=Σ_d O_id*dO_id，结果是一行一个标量；它等于该行 Σ_j P_ij*dP_ij。
-• [T#B#恢复概率]：用 Q/K 重算自然分数 S，再换成 x=S/ln2，以 P=2^(x−M) 恢复对应概率。M 保存的是完整分母的 log₂，不能把它当成仅有行最大值。
-• [T#B#反向链]：由 O=PV 得到 dP=dOVᵀ 和 dV=PᵀdO，再令 G=P⊙(dP−Delta)，即对自然分数 S=sQKᵀ 的梯度，得到 dQ=sGK、dK=sGᵀQ。这里 s 为固定的原始 scale。
-• [T#B#输出所有权]：dQ 固定 query 并沿 key 汇总；dK/dV 固定 key 并沿 query 汇总。一个 program 算齐自己的输出块后独占写回，所以这种分工不需要跨 program atomic。
-[T#B,!c47f17#边界]：前向保存量、反向临时量和最终梯度的产生时间不同。若把同一输出块的归约拆给多个 program，就必须另行合并部分贡献。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：反向用前向保存量和 dO 按块重建概率，再按各个梯度的归约方向分工，全程不物化 N×N 矩阵。
+• [T#B#保存与准备]：前向保存 Q/K/V/O/M，dQ/dK/dV 是反向才产生的输出。预处理对每个 query 沿特征维算 Delta_i=Σ_d O_id·dO_id，一行一个标量。
+• [T#B#恢复概率]：用 Q/K 重算分数并换到 exp2 域 x=S/ln2，再以 P=2^(x−M) 恢复概率；M 是完整分母的 log₂，不只是行最大值。
+• [T#B#梯度链]：dV=PᵀdO，dP=dO·Vᵀ；对自然分数 S 的梯度 G=P⊙(dP−Delta)；dQ=s·G·K，dK=s·Gᵀ·Q，s 为原始 scale。
+• [T#B#输出所有权]：dK/dV 固定 key、沿 query 汇总，dQ=s·G·K 则固定 query、沿 key 汇总；一个 program 算齐自己的输出块后独占写回，不需要 atomic。
+[T#B,!c47f17#边界]：若把同一输出块的归约拆给多个 program，就要另外合并部分贡献。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">按产生时间区分前向保存量、反向临时量与最终梯度；说明Delta沿特征维求和且每query一个值；说明M重建概率而非只代替行最大值；完整说明dP、softmax分数梯度和三个输入梯度的关系；把归约方向与单program完整归约、独占写回联系起来</t>
+          <t xml:space="preserve">区分前向保存的 Q/K/V/O/M、反向临时量与最终梯度；说明 Delta 沿特征维求和、每个 query 一个值；说明用 M 重建概率，且 M 不只是行最大值；说出 G=P⊙(dP−Delta)，以及 dQ/dK/dV 各由哪两个量相乘；把归约方向与单 program 完整归约、独占写回联系起来</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
